--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123260452</v>
+        <v>123260481</v>
       </c>
       <c r="B2" t="n">
         <v>90970</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
+          <t>Bleckåsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437859</v>
+        <v>437726</v>
       </c>
       <c r="R2" t="n">
-        <v>7028230</v>
+        <v>7028272</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123260481</v>
+        <v>123260452</v>
       </c>
       <c r="B3" t="n">
         <v>90970</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Jmt</t>
+          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437726</v>
+        <v>437859</v>
       </c>
       <c r="R3" t="n">
-        <v>7028272</v>
+        <v>7028230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123260481</v>
+        <v>123260452</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Jmt</t>
+          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437726</v>
+        <v>437859</v>
       </c>
       <c r="R2" t="n">
-        <v>7028272</v>
+        <v>7028230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123260452</v>
+        <v>123260481</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
+          <t>Bleckåsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437859</v>
+        <v>437726</v>
       </c>
       <c r="R3" t="n">
-        <v>7028230</v>
+        <v>7028272</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123260452</v>
       </c>
       <c r="B2" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>123260481</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123260452</v>
+        <v>123260481</v>
       </c>
       <c r="B2" t="n">
-        <v>90975</v>
+        <v>90981</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
+          <t>Bleckåsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437859</v>
+        <v>437726</v>
       </c>
       <c r="R2" t="n">
-        <v>7028230</v>
+        <v>7028272</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123260481</v>
+        <v>123260452</v>
       </c>
       <c r="B3" t="n">
-        <v>90975</v>
+        <v>90981</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Jmt</t>
+          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437726</v>
+        <v>437859</v>
       </c>
       <c r="R3" t="n">
-        <v>7028272</v>
+        <v>7028230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123260481</v>
       </c>
       <c r="B2" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>123260452</v>
       </c>
       <c r="B3" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123260481</v>
+        <v>123260452</v>
       </c>
       <c r="B2" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Jmt</t>
+          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437726</v>
+        <v>437859</v>
       </c>
       <c r="R2" t="n">
-        <v>7028272</v>
+        <v>7028230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123260452</v>
+        <v>123260481</v>
       </c>
       <c r="B3" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
+          <t>Bleckåsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437859</v>
+        <v>437726</v>
       </c>
       <c r="R3" t="n">
-        <v>7028230</v>
+        <v>7028272</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123260452</v>
+        <v>123260481</v>
       </c>
       <c r="B2" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
+          <t>Bleckåsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437859</v>
+        <v>437726</v>
       </c>
       <c r="R2" t="n">
-        <v>7028230</v>
+        <v>7028272</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123260481</v>
+        <v>123260452</v>
       </c>
       <c r="B3" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Jmt</t>
+          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437726</v>
+        <v>437859</v>
       </c>
       <c r="R3" t="n">
-        <v>7028272</v>
+        <v>7028230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123260481</v>
       </c>
       <c r="B2" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>123260452</v>
       </c>
       <c r="B3" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123260481</v>
+        <v>123260452</v>
       </c>
       <c r="B2" t="n">
         <v>91008</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Jmt</t>
+          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437726</v>
+        <v>437859</v>
       </c>
       <c r="R2" t="n">
-        <v>7028272</v>
+        <v>7028230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123260452</v>
+        <v>123260481</v>
       </c>
       <c r="B3" t="n">
         <v>91008</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
+          <t>Bleckåsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437859</v>
+        <v>437726</v>
       </c>
       <c r="R3" t="n">
-        <v>7028230</v>
+        <v>7028272</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123260452</v>
+        <v>123260481</v>
       </c>
       <c r="B2" t="n">
         <v>91008</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
+          <t>Bleckåsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437859</v>
+        <v>437726</v>
       </c>
       <c r="R2" t="n">
-        <v>7028230</v>
+        <v>7028272</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123260481</v>
+        <v>123260452</v>
       </c>
       <c r="B3" t="n">
         <v>91008</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bleckåsbacken, Jmt</t>
+          <t>Bleckåsbacken, Bleckåsen, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437726</v>
+        <v>437859</v>
       </c>
       <c r="R3" t="n">
-        <v>7028272</v>
+        <v>7028230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124138438</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bleckåsen SV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>437572</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7028158</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,6 +1008,2635 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124804266</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95335</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>437728</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7028259</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124805471</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78891</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>437816</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7028222</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124804665</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>437783</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7028272</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124804327</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>437725</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7028254</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124805623</v>
+      </c>
+      <c r="B9" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>437770</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7028132</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På marken i rikare gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124804429</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>437740</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7028260</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124804113</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>437748</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7028228</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124805275</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>437805</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7028276</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124803959</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>437775</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7028228</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124803570</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>437812</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7028208</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På död gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124805701</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79280</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1797</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mjölig dropplav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cliostomum leprosum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>437772</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7028134</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124804385</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91457</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>437727</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7028271</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal bördig granskog</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124803850</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91950</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>437757</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7028220</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124804567</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>437764</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7028274</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124805365</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91950</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>437833</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7028238</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124804248</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95347</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>437722</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7028264</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124805601</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>437787</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7028156</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124806116</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>437748</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7028199</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124805959</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78891</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>283</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>437768</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7028160</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124803938</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78891</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>283</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>437774</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7028215</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124803330</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95335</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>437842</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7028204</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog i nordsluttning</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124803467</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>437836</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7028199</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124804266</v>
+        <v>124805601</v>
       </c>
       <c r="B5" t="n">
-        <v>95335</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,38 +1022,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437728</v>
+        <v>437787</v>
       </c>
       <c r="R5" t="n">
-        <v>7028259</v>
+        <v>7028156</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124805471</v>
+        <v>124804665</v>
       </c>
       <c r="B6" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,26 +1148,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1176,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437816</v>
+        <v>437783</v>
       </c>
       <c r="R6" t="n">
-        <v>7028222</v>
+        <v>7028272</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,12 +1226,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804665</v>
+        <v>124806116</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,43 +1274,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437783</v>
+        <v>437748</v>
       </c>
       <c r="R7" t="n">
-        <v>7028272</v>
+        <v>7028199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,12 +1343,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804327</v>
+        <v>124804385</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,25 +1387,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1419,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437725</v>
+        <v>437727</v>
       </c>
       <c r="R8" t="n">
-        <v>7028254</v>
+        <v>7028271</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,12 +1460,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124805623</v>
+        <v>124805365</v>
       </c>
       <c r="B9" t="n">
-        <v>105102</v>
+        <v>91950</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,21 +1508,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1536,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437770</v>
+        <v>437833</v>
       </c>
       <c r="R9" t="n">
-        <v>7028132</v>
+        <v>7028238</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,12 +1577,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124804429</v>
+        <v>124803850</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,25 +1621,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437740</v>
+        <v>437757</v>
       </c>
       <c r="R10" t="n">
-        <v>7028260</v>
+        <v>7028220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,12 +1694,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804113</v>
+        <v>124805471</v>
       </c>
       <c r="B11" t="n">
-        <v>105102</v>
+        <v>78891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,31 +1738,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437748</v>
+        <v>437816</v>
       </c>
       <c r="R11" t="n">
-        <v>7028228</v>
+        <v>7028222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124805275</v>
+        <v>124803467</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,47 +1864,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437805</v>
+        <v>437836</v>
       </c>
       <c r="R12" t="n">
-        <v>7028276</v>
+        <v>7028199</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,12 +1937,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124803959</v>
+        <v>124805275</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,34 +1985,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437775</v>
+        <v>437805</v>
       </c>
       <c r="R13" t="n">
-        <v>7028228</v>
+        <v>7028276</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,7 +2095,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803570</v>
+        <v>124803959</v>
       </c>
       <c r="B14" t="n">
         <v>91030</v>
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437812</v>
+        <v>437775</v>
       </c>
       <c r="R14" t="n">
-        <v>7028208</v>
+        <v>7028228</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2212,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124805701</v>
+        <v>124804248</v>
       </c>
       <c r="B15" t="n">
-        <v>79280</v>
+        <v>95347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,25 +2224,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1797</v>
+        <v>2813</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437772</v>
+        <v>437722</v>
       </c>
       <c r="R15" t="n">
-        <v>7028134</v>
+        <v>7028264</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2329,10 +2329,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124804385</v>
+        <v>124805623</v>
       </c>
       <c r="B16" t="n">
-        <v>91457</v>
+        <v>105102</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,25 +2341,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437727</v>
+        <v>437770</v>
       </c>
       <c r="R16" t="n">
-        <v>7028271</v>
+        <v>7028132</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,10 +2446,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124803850</v>
+        <v>124803330</v>
       </c>
       <c r="B17" t="n">
-        <v>91950</v>
+        <v>95335</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2486,13 +2486,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437757</v>
+        <v>437842</v>
       </c>
       <c r="R17" t="n">
-        <v>7028220</v>
+        <v>7028204</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2563,7 +2563,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124804567</v>
+        <v>124804327</v>
       </c>
       <c r="B18" t="n">
         <v>91030</v>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437764</v>
+        <v>437725</v>
       </c>
       <c r="R18" t="n">
-        <v>7028274</v>
+        <v>7028254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124805365</v>
+        <v>124804266</v>
       </c>
       <c r="B19" t="n">
-        <v>91950</v>
+        <v>95335</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437833</v>
+        <v>437728</v>
       </c>
       <c r="R19" t="n">
-        <v>7028238</v>
+        <v>7028259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2797,10 +2797,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804248</v>
+        <v>124803938</v>
       </c>
       <c r="B20" t="n">
-        <v>95347</v>
+        <v>78891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2809,38 +2809,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2813</v>
+        <v>283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437722</v>
+        <v>437774</v>
       </c>
       <c r="R20" t="n">
-        <v>7028264</v>
+        <v>7028215</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2872,7 +2881,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2882,12 +2891,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2914,10 +2923,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124805601</v>
+        <v>124803570</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2930,39 +2939,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437787</v>
+        <v>437812</v>
       </c>
       <c r="R21" t="n">
-        <v>7028156</v>
+        <v>7028208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2994,7 +2998,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,12 +3008,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,10 +3040,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124806116</v>
+        <v>124805701</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>79280</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3052,21 +3056,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3076,10 +3080,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437748</v>
+        <v>437772</v>
       </c>
       <c r="R22" t="n">
-        <v>7028199</v>
+        <v>7028134</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3111,7 +3115,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3121,12 +3125,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,10 +3283,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124803938</v>
+        <v>124804567</v>
       </c>
       <c r="B24" t="n">
-        <v>78891</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3295,43 +3299,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437774</v>
+        <v>437764</v>
       </c>
       <c r="R24" t="n">
-        <v>7028215</v>
+        <v>7028274</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3363,7 +3358,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3373,12 +3368,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3405,10 +3400,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124803330</v>
+        <v>124804113</v>
       </c>
       <c r="B25" t="n">
-        <v>95335</v>
+        <v>105102</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3421,37 +3416,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437842</v>
+        <v>437748</v>
       </c>
       <c r="R25" t="n">
-        <v>7028204</v>
+        <v>7028228</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3522,10 +3522,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124803467</v>
+        <v>124804429</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3534,25 +3534,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437836</v>
+        <v>437740</v>
       </c>
       <c r="R26" t="n">
-        <v>7028199</v>
+        <v>7028260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805601</v>
+        <v>124803850</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,43 +1022,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437787</v>
+        <v>437757</v>
       </c>
       <c r="R5" t="n">
-        <v>7028156</v>
+        <v>7028220</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124804665</v>
+        <v>124805959</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,26 +1143,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1181,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437783</v>
+        <v>437768</v>
       </c>
       <c r="R6" t="n">
-        <v>7028272</v>
+        <v>7028160</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,12 +1221,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124806116</v>
+        <v>124803959</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437748</v>
+        <v>437775</v>
       </c>
       <c r="R7" t="n">
-        <v>7028199</v>
+        <v>7028228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1338,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804385</v>
+        <v>124803467</v>
       </c>
       <c r="B8" t="n">
-        <v>91457</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,25 +1382,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437727</v>
+        <v>437836</v>
       </c>
       <c r="R8" t="n">
-        <v>7028271</v>
+        <v>7028199</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,12 +1455,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124805365</v>
+        <v>124804327</v>
       </c>
       <c r="B9" t="n">
-        <v>91950</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,25 +1499,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437833</v>
+        <v>437725</v>
       </c>
       <c r="R9" t="n">
-        <v>7028238</v>
+        <v>7028254</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,12 +1572,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124803850</v>
+        <v>124805601</v>
       </c>
       <c r="B10" t="n">
-        <v>91950</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,38 +1616,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437757</v>
+        <v>437787</v>
       </c>
       <c r="R10" t="n">
-        <v>7028220</v>
+        <v>7028156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124805471</v>
+        <v>124804429</v>
       </c>
       <c r="B11" t="n">
-        <v>78891</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,43 +1742,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437816</v>
+        <v>437740</v>
       </c>
       <c r="R11" t="n">
-        <v>7028222</v>
+        <v>7028260</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,12 +1811,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803467</v>
+        <v>124806116</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,25 +1855,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1892,7 +1883,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437836</v>
+        <v>437748</v>
       </c>
       <c r="R12" t="n">
         <v>7028199</v>
@@ -1927,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1969,10 +1960,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124805275</v>
+        <v>124803570</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,43 +1976,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437805</v>
+        <v>437812</v>
       </c>
       <c r="R13" t="n">
-        <v>7028276</v>
+        <v>7028208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2035,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,12 +2045,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803959</v>
+        <v>124805471</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2111,34 +2093,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437775</v>
+        <v>437816</v>
       </c>
       <c r="R14" t="n">
-        <v>7028228</v>
+        <v>7028222</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2161,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,12 +2171,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2212,10 +2203,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124804248</v>
+        <v>124805623</v>
       </c>
       <c r="B15" t="n">
-        <v>95347</v>
+        <v>105102</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,21 +2219,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2813</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2243,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437722</v>
+        <v>437770</v>
       </c>
       <c r="R15" t="n">
-        <v>7028264</v>
+        <v>7028132</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,7 +2278,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2288,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2329,10 +2320,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124805623</v>
+        <v>124805701</v>
       </c>
       <c r="B16" t="n">
-        <v>105102</v>
+        <v>79280</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,25 +2332,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>1797</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2369,10 +2360,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437770</v>
+        <v>437772</v>
       </c>
       <c r="R16" t="n">
-        <v>7028132</v>
+        <v>7028134</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2404,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,12 +2405,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,10 +2437,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124803330</v>
+        <v>124804113</v>
       </c>
       <c r="B17" t="n">
-        <v>95335</v>
+        <v>105102</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2462,37 +2453,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437842</v>
+        <v>437748</v>
       </c>
       <c r="R17" t="n">
-        <v>7028204</v>
+        <v>7028228</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2521,7 +2517,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2531,12 +2527,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2563,10 +2559,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124804327</v>
+        <v>124804248</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>95347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2575,25 +2571,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>2813</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2603,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437725</v>
+        <v>437722</v>
       </c>
       <c r="R18" t="n">
-        <v>7028254</v>
+        <v>7028264</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2638,7 +2634,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2648,12 +2644,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2797,10 +2793,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124803938</v>
+        <v>124805365</v>
       </c>
       <c r="B20" t="n">
-        <v>78891</v>
+        <v>91950</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2809,47 +2805,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437774</v>
+        <v>437833</v>
       </c>
       <c r="R20" t="n">
-        <v>7028215</v>
+        <v>7028238</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2881,7 +2868,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2891,12 +2878,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2923,10 +2910,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124803570</v>
+        <v>124805275</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2939,34 +2926,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437812</v>
+        <v>437805</v>
       </c>
       <c r="R21" t="n">
-        <v>7028208</v>
+        <v>7028276</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2998,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3008,12 +3004,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3040,10 +3036,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124805701</v>
+        <v>124803938</v>
       </c>
       <c r="B22" t="n">
-        <v>79280</v>
+        <v>78891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3056,34 +3052,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1797</v>
+        <v>283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437772</v>
+        <v>437774</v>
       </c>
       <c r="R22" t="n">
-        <v>7028134</v>
+        <v>7028215</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3115,7 +3120,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3125,12 +3130,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3157,10 +3162,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124805959</v>
+        <v>124804385</v>
       </c>
       <c r="B23" t="n">
-        <v>78891</v>
+        <v>91457</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3169,50 +3174,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437768</v>
+        <v>437727</v>
       </c>
       <c r="R23" t="n">
-        <v>7028160</v>
+        <v>7028271</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3241,7 +3237,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3251,12 +3247,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3283,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124804567</v>
+        <v>124803330</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>95335</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3295,25 +3291,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3323,13 +3319,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437764</v>
+        <v>437842</v>
       </c>
       <c r="R24" t="n">
-        <v>7028274</v>
+        <v>7028204</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3358,7 +3354,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3368,12 +3364,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3400,10 +3396,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124804113</v>
+        <v>124804665</v>
       </c>
       <c r="B25" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,31 +3408,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437748</v>
+        <v>437783</v>
       </c>
       <c r="R25" t="n">
-        <v>7028228</v>
+        <v>7028272</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3522,10 +3522,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124804429</v>
+        <v>124804567</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3538,21 +3538,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437740</v>
+        <v>437764</v>
       </c>
       <c r="R26" t="n">
-        <v>7028260</v>
+        <v>7028274</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124805959</v>
+        <v>124803959</v>
       </c>
       <c r="B6" t="n">
-        <v>78891</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,46 +1143,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437768</v>
+        <v>437775</v>
       </c>
       <c r="R6" t="n">
-        <v>7028160</v>
+        <v>7028228</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,12 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803959</v>
+        <v>124803467</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437775</v>
+        <v>437836</v>
       </c>
       <c r="R7" t="n">
-        <v>7028228</v>
+        <v>7028199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,12 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124803467</v>
+        <v>124805959</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>78891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,41 +1373,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437836</v>
+        <v>437768</v>
       </c>
       <c r="R8" t="n">
-        <v>7028199</v>
+        <v>7028160</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1960,10 +1960,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124803570</v>
+        <v>124805471</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>78891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1976,34 +1976,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437812</v>
+        <v>437816</v>
       </c>
       <c r="R13" t="n">
-        <v>7028208</v>
+        <v>7028222</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2045,12 +2054,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,10 +2086,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124805471</v>
+        <v>124803570</v>
       </c>
       <c r="B14" t="n">
-        <v>78891</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,43 +2102,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437816</v>
+        <v>437812</v>
       </c>
       <c r="R14" t="n">
-        <v>7028222</v>
+        <v>7028208</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124804665</v>
+        <v>124804567</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,43 +3412,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437783</v>
+        <v>437764</v>
       </c>
       <c r="R25" t="n">
-        <v>7028272</v>
+        <v>7028274</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3480,7 +3471,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3490,12 +3481,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3522,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124804567</v>
+        <v>124804665</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3538,34 +3529,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437764</v>
+        <v>437783</v>
       </c>
       <c r="R26" t="n">
-        <v>7028274</v>
+        <v>7028272</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -910,7 +910,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124803959</v>
+        <v>124805959</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>78891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,37 +1143,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437775</v>
+        <v>437768</v>
       </c>
       <c r="R6" t="n">
-        <v>7028228</v>
+        <v>7028160</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1221,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803467</v>
+        <v>124803959</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,25 +1265,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437836</v>
+        <v>437775</v>
       </c>
       <c r="R7" t="n">
-        <v>7028199</v>
+        <v>7028228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1338,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124805959</v>
+        <v>124803467</v>
       </c>
       <c r="B8" t="n">
-        <v>78891</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,50 +1382,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>283</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437768</v>
+        <v>437836</v>
       </c>
       <c r="R8" t="n">
-        <v>7028160</v>
+        <v>7028199</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124804567</v>
+        <v>124804665</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,34 +3412,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437764</v>
+        <v>437783</v>
       </c>
       <c r="R25" t="n">
-        <v>7028274</v>
+        <v>7028272</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,7 +3480,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3481,12 +3490,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3513,10 +3522,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124804665</v>
+        <v>124804567</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,43 +3538,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437783</v>
+        <v>437764</v>
       </c>
       <c r="R26" t="n">
-        <v>7028272</v>
+        <v>7028274</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,50 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138438</v>
+        <v>124804385</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437572</v>
+        <v>437727</v>
       </c>
       <c r="R4" t="n">
-        <v>7028158</v>
+        <v>7028271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,17 +973,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124803850</v>
+        <v>124803959</v>
       </c>
       <c r="B5" t="n">
-        <v>91950</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437757</v>
+        <v>437775</v>
       </c>
       <c r="R5" t="n">
-        <v>7028220</v>
+        <v>7028228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124805959</v>
+        <v>124803330</v>
       </c>
       <c r="B6" t="n">
-        <v>78891</v>
+        <v>95335</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,50 +1149,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437768</v>
+        <v>437842</v>
       </c>
       <c r="R6" t="n">
-        <v>7028160</v>
+        <v>7028204</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,12 +1222,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803959</v>
+        <v>124804113</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,35 +1266,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437775</v>
+        <v>437748</v>
       </c>
       <c r="R7" t="n">
         <v>7028228</v>
@@ -1328,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,12 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124803467</v>
+        <v>124805601</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,38 +1388,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437836</v>
+        <v>437787</v>
       </c>
       <c r="R8" t="n">
-        <v>7028199</v>
+        <v>7028156</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,12 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124804327</v>
+        <v>124803938</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>78891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,34 +1514,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437725</v>
+        <v>437774</v>
       </c>
       <c r="R9" t="n">
-        <v>7028254</v>
+        <v>7028215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,12 +1592,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124805601</v>
+        <v>124805365</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,43 +1636,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437787</v>
+        <v>437833</v>
       </c>
       <c r="R10" t="n">
-        <v>7028156</v>
+        <v>7028238</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,12 +1709,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804429</v>
+        <v>124805275</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,34 +1757,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437740</v>
+        <v>437805</v>
       </c>
       <c r="R11" t="n">
-        <v>7028260</v>
+        <v>7028276</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1825,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1811,12 +1835,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124806116</v>
+        <v>124803467</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,7 +1907,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437748</v>
+        <v>437836</v>
       </c>
       <c r="R12" t="n">
         <v>7028199</v>
@@ -1918,7 +1942,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1952,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1960,7 +1984,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124805471</v>
+        <v>124805959</v>
       </c>
       <c r="B13" t="n">
         <v>78891</v>
@@ -1995,7 +2019,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2009,13 +2033,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437816</v>
+        <v>437768</v>
       </c>
       <c r="R13" t="n">
-        <v>7028222</v>
+        <v>7028160</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2044,7 +2068,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,12 +2078,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803570</v>
+        <v>124803850</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>91950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,25 +2122,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2126,10 +2150,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437812</v>
+        <v>437757</v>
       </c>
       <c r="R14" t="n">
-        <v>7028208</v>
+        <v>7028220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,7 +2185,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,12 +2195,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2203,10 +2227,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124805623</v>
+        <v>124805701</v>
       </c>
       <c r="B15" t="n">
-        <v>105102</v>
+        <v>79280</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,25 +2239,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>1797</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2243,10 +2267,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437770</v>
+        <v>437772</v>
       </c>
       <c r="R15" t="n">
-        <v>7028132</v>
+        <v>7028134</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2278,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2288,12 +2312,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2320,10 +2344,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124805701</v>
+        <v>124804266</v>
       </c>
       <c r="B16" t="n">
-        <v>79280</v>
+        <v>95335</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2332,25 +2356,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1797</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2360,10 +2384,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437772</v>
+        <v>437728</v>
       </c>
       <c r="R16" t="n">
-        <v>7028134</v>
+        <v>7028259</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,7 +2419,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,12 +2429,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2437,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124804113</v>
+        <v>124804327</v>
       </c>
       <c r="B17" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,43 +2473,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437748</v>
+        <v>437725</v>
       </c>
       <c r="R17" t="n">
-        <v>7028228</v>
+        <v>7028254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2517,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2527,12 +2546,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2559,10 +2578,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124804248</v>
+        <v>124805471</v>
       </c>
       <c r="B18" t="n">
-        <v>95347</v>
+        <v>78891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2571,38 +2590,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2813</v>
+        <v>283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437722</v>
+        <v>437816</v>
       </c>
       <c r="R18" t="n">
-        <v>7028264</v>
+        <v>7028222</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2644,12 +2672,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124804266</v>
+        <v>124805623</v>
       </c>
       <c r="B19" t="n">
-        <v>95335</v>
+        <v>105102</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,21 +2720,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2716,10 +2744,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437728</v>
+        <v>437770</v>
       </c>
       <c r="R19" t="n">
-        <v>7028259</v>
+        <v>7028132</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2751,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2761,12 +2789,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124805365</v>
+        <v>124803570</v>
       </c>
       <c r="B20" t="n">
-        <v>91950</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2805,25 +2833,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2833,10 +2861,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437833</v>
+        <v>437812</v>
       </c>
       <c r="R20" t="n">
-        <v>7028238</v>
+        <v>7028208</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2878,12 +2906,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2910,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124805275</v>
+        <v>124804248</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>95347</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2922,47 +2950,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437805</v>
+        <v>437722</v>
       </c>
       <c r="R21" t="n">
-        <v>7028276</v>
+        <v>7028264</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2994,7 +3013,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,12 +3023,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,10 +3055,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124803938</v>
+        <v>124806116</v>
       </c>
       <c r="B22" t="n">
-        <v>78891</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3052,43 +3071,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437774</v>
+        <v>437748</v>
       </c>
       <c r="R22" t="n">
-        <v>7028215</v>
+        <v>7028199</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3120,7 +3130,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3130,12 +3140,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3162,10 +3172,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804385</v>
+        <v>124804567</v>
       </c>
       <c r="B23" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3174,25 +3184,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3202,10 +3212,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437727</v>
+        <v>437764</v>
       </c>
       <c r="R23" t="n">
-        <v>7028271</v>
+        <v>7028274</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3237,7 +3247,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3247,12 +3257,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3279,10 +3289,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124803330</v>
+        <v>124804665</v>
       </c>
       <c r="B24" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,41 +3301,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437842</v>
+        <v>437783</v>
       </c>
       <c r="R24" t="n">
-        <v>7028204</v>
+        <v>7028272</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3354,7 +3373,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3364,12 +3383,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3396,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124804665</v>
+        <v>124804429</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,43 +3431,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437783</v>
+        <v>437740</v>
       </c>
       <c r="R25" t="n">
-        <v>7028272</v>
+        <v>7028260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3480,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3490,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3522,14 +3532,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124804567</v>
+        <v>124138438</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3538,34 +3548,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437764</v>
+        <v>437572</v>
       </c>
       <c r="R26" t="n">
-        <v>7028274</v>
+        <v>7028158</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3592,27 +3602,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3627,12 +3627,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124804385</v>
+        <v>124803570</v>
       </c>
       <c r="B4" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437727</v>
+        <v>437812</v>
       </c>
       <c r="R4" t="n">
-        <v>7028271</v>
+        <v>7028208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124803959</v>
+        <v>124805601</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1036,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437775</v>
+        <v>437787</v>
       </c>
       <c r="R5" t="n">
-        <v>7028228</v>
+        <v>7028156</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124803330</v>
+        <v>124803959</v>
       </c>
       <c r="B6" t="n">
-        <v>95335</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,25 +1154,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,13 +1182,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437842</v>
+        <v>437775</v>
       </c>
       <c r="R6" t="n">
-        <v>7028204</v>
+        <v>7028228</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804113</v>
+        <v>124803467</v>
       </c>
       <c r="B7" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,39 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437748</v>
+        <v>437836</v>
       </c>
       <c r="R7" t="n">
-        <v>7028228</v>
+        <v>7028199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124805601</v>
+        <v>124804385</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,43 +1388,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437787</v>
+        <v>437727</v>
       </c>
       <c r="R8" t="n">
-        <v>7028156</v>
+        <v>7028271</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124803938</v>
+        <v>124805471</v>
       </c>
       <c r="B9" t="n">
         <v>78891</v>
@@ -1533,7 +1528,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1547,10 +1542,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437774</v>
+        <v>437816</v>
       </c>
       <c r="R9" t="n">
-        <v>7028215</v>
+        <v>7028222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,12 +1587,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124805365</v>
+        <v>124805959</v>
       </c>
       <c r="B10" t="n">
-        <v>91950</v>
+        <v>78891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,41 +1631,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437833</v>
+        <v>437768</v>
       </c>
       <c r="R10" t="n">
-        <v>7028238</v>
+        <v>7028160</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1699,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,12 +1713,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124805275</v>
+        <v>124804248</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>95347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,47 +1757,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437805</v>
+        <v>437722</v>
       </c>
       <c r="R11" t="n">
-        <v>7028276</v>
+        <v>7028264</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,12 +1830,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803467</v>
+        <v>124806116</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1874,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,7 +1902,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437836</v>
+        <v>437748</v>
       </c>
       <c r="R12" t="n">
         <v>7028199</v>
@@ -1942,7 +1937,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1952,7 +1947,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1984,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124805959</v>
+        <v>124805365</v>
       </c>
       <c r="B13" t="n">
-        <v>78891</v>
+        <v>91950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,50 +1991,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437768</v>
+        <v>437833</v>
       </c>
       <c r="R13" t="n">
-        <v>7028160</v>
+        <v>7028238</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,7 +2054,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2078,12 +2064,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803850</v>
+        <v>124803938</v>
       </c>
       <c r="B14" t="n">
-        <v>91950</v>
+        <v>78891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2122,38 +2108,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437757</v>
+        <v>437774</v>
       </c>
       <c r="R14" t="n">
-        <v>7028220</v>
+        <v>7028215</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2195,12 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2227,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124805701</v>
+        <v>124805275</v>
       </c>
       <c r="B15" t="n">
-        <v>79280</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2243,34 +2238,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437772</v>
+        <v>437805</v>
       </c>
       <c r="R15" t="n">
-        <v>7028134</v>
+        <v>7028276</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,7 +2306,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,12 +2316,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,10 +2348,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124804266</v>
+        <v>124804567</v>
       </c>
       <c r="B16" t="n">
-        <v>95335</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2356,25 +2360,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2384,10 +2388,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437728</v>
+        <v>437764</v>
       </c>
       <c r="R16" t="n">
-        <v>7028259</v>
+        <v>7028274</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2419,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2429,12 +2433,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2461,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124804327</v>
+        <v>124804113</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,38 +2477,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437725</v>
+        <v>437748</v>
       </c>
       <c r="R17" t="n">
-        <v>7028254</v>
+        <v>7028228</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2536,7 +2545,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,12 +2555,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2578,10 +2587,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124805471</v>
+        <v>124803850</v>
       </c>
       <c r="B18" t="n">
-        <v>78891</v>
+        <v>91950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2590,47 +2599,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437816</v>
+        <v>437757</v>
       </c>
       <c r="R18" t="n">
-        <v>7028222</v>
+        <v>7028220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2821,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124803570</v>
+        <v>124805701</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>79280</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1797</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437812</v>
+        <v>437772</v>
       </c>
       <c r="R20" t="n">
-        <v>7028208</v>
+        <v>7028134</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124804248</v>
+        <v>124804665</v>
       </c>
       <c r="B21" t="n">
-        <v>95347</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2950,38 +2950,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437722</v>
+        <v>437783</v>
       </c>
       <c r="R21" t="n">
-        <v>7028264</v>
+        <v>7028272</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3013,7 +3022,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3023,12 +3032,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,7 +3064,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124806116</v>
+        <v>124804429</v>
       </c>
       <c r="B22" t="n">
         <v>91012</v>
@@ -3095,10 +3104,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437748</v>
+        <v>437740</v>
       </c>
       <c r="R22" t="n">
-        <v>7028199</v>
+        <v>7028260</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3130,7 +3139,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3140,7 +3149,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3172,7 +3181,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804567</v>
+        <v>124804327</v>
       </c>
       <c r="B23" t="n">
         <v>91030</v>
@@ -3212,10 +3221,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437764</v>
+        <v>437725</v>
       </c>
       <c r="R23" t="n">
-        <v>7028274</v>
+        <v>7028254</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3247,7 +3256,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3257,12 +3266,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,10 +3298,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124804665</v>
+        <v>124803330</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3301,50 +3310,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437783</v>
+        <v>437842</v>
       </c>
       <c r="R24" t="n">
-        <v>7028272</v>
+        <v>7028204</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124804429</v>
+        <v>124804266</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>95335</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3427,25 +3427,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437740</v>
+        <v>437728</v>
       </c>
       <c r="R25" t="n">
-        <v>7028260</v>
+        <v>7028259</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124803570</v>
+        <v>124805471</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>78891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +919,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437812</v>
+        <v>437816</v>
       </c>
       <c r="R4" t="n">
-        <v>7028208</v>
+        <v>7028222</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805601</v>
+        <v>124804327</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,39 +1045,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437787</v>
+        <v>437725</v>
       </c>
       <c r="R5" t="n">
-        <v>7028156</v>
+        <v>7028254</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124803959</v>
+        <v>124803330</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>95335</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,25 +1158,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437775</v>
+        <v>437842</v>
       </c>
       <c r="R6" t="n">
-        <v>7028228</v>
+        <v>7028204</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1231,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803467</v>
+        <v>124804113</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>105102</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,34 +1279,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437836</v>
+        <v>437748</v>
       </c>
       <c r="R7" t="n">
-        <v>7028199</v>
+        <v>7028228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804385</v>
+        <v>124805275</v>
       </c>
       <c r="B8" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,38 +1397,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437727</v>
+        <v>437805</v>
       </c>
       <c r="R8" t="n">
-        <v>7028271</v>
+        <v>7028276</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1479,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124805471</v>
+        <v>124803850</v>
       </c>
       <c r="B9" t="n">
-        <v>78891</v>
+        <v>91950</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,47 +1523,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437816</v>
+        <v>437757</v>
       </c>
       <c r="R9" t="n">
-        <v>7028222</v>
+        <v>7028220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,12 +1596,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124805959</v>
+        <v>124805701</v>
       </c>
       <c r="B10" t="n">
-        <v>78891</v>
+        <v>79280</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,46 +1644,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>283</v>
+        <v>1797</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437768</v>
+        <v>437772</v>
       </c>
       <c r="R10" t="n">
-        <v>7028160</v>
+        <v>7028134</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804248</v>
+        <v>124803938</v>
       </c>
       <c r="B11" t="n">
-        <v>95347</v>
+        <v>78891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,38 +1757,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2813</v>
+        <v>283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437722</v>
+        <v>437774</v>
       </c>
       <c r="R11" t="n">
-        <v>7028264</v>
+        <v>7028215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1829,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1839,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124806116</v>
+        <v>124803570</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,21 +1887,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1902,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437748</v>
+        <v>437812</v>
       </c>
       <c r="R12" t="n">
-        <v>7028199</v>
+        <v>7028208</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,7 +1946,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1947,12 +1956,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,10 +1988,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124805365</v>
+        <v>124803959</v>
       </c>
       <c r="B13" t="n">
-        <v>91950</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1991,25 +2000,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +2028,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437833</v>
+        <v>437775</v>
       </c>
       <c r="R13" t="n">
-        <v>7028238</v>
+        <v>7028228</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2064,12 +2073,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,10 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803938</v>
+        <v>124804429</v>
       </c>
       <c r="B14" t="n">
-        <v>78891</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2112,43 +2121,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437774</v>
+        <v>437740</v>
       </c>
       <c r="R14" t="n">
-        <v>7028215</v>
+        <v>7028260</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124805275</v>
+        <v>124803467</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,47 +2234,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437805</v>
+        <v>437836</v>
       </c>
       <c r="R15" t="n">
-        <v>7028276</v>
+        <v>7028199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2306,7 +2297,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2316,12 +2307,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2348,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124804567</v>
+        <v>124805601</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2364,34 +2355,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437764</v>
+        <v>437787</v>
       </c>
       <c r="R16" t="n">
-        <v>7028274</v>
+        <v>7028156</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2423,7 +2419,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2433,12 +2429,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2465,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124804113</v>
+        <v>124804567</v>
       </c>
       <c r="B17" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,43 +2473,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437748</v>
+        <v>437764</v>
       </c>
       <c r="R17" t="n">
-        <v>7028228</v>
+        <v>7028274</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2545,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2555,12 +2546,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2587,10 +2578,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124803850</v>
+        <v>124804248</v>
       </c>
       <c r="B18" t="n">
-        <v>91950</v>
+        <v>95347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2603,21 +2594,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>2813</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2627,10 +2618,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437757</v>
+        <v>437722</v>
       </c>
       <c r="R18" t="n">
-        <v>7028220</v>
+        <v>7028264</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,7 +2663,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2704,10 +2695,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124805623</v>
+        <v>124804385</v>
       </c>
       <c r="B19" t="n">
-        <v>105102</v>
+        <v>91457</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2716,25 +2707,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2744,10 +2735,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437770</v>
+        <v>437727</v>
       </c>
       <c r="R19" t="n">
-        <v>7028132</v>
+        <v>7028271</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2770,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2780,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2821,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124805701</v>
+        <v>124804266</v>
       </c>
       <c r="B20" t="n">
-        <v>79280</v>
+        <v>95335</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2833,25 +2824,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1797</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2861,10 +2852,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437772</v>
+        <v>437728</v>
       </c>
       <c r="R20" t="n">
-        <v>7028134</v>
+        <v>7028259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2896,7 +2887,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2906,12 +2897,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,10 +2929,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124804665</v>
+        <v>124805365</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91950</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2950,47 +2941,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437783</v>
+        <v>437833</v>
       </c>
       <c r="R21" t="n">
-        <v>7028272</v>
+        <v>7028238</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,7 +3004,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3032,12 +3014,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,10 +3046,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124804429</v>
+        <v>124805959</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>78891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3080,37 +3062,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437740</v>
+        <v>437768</v>
       </c>
       <c r="R22" t="n">
-        <v>7028260</v>
+        <v>7028160</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3139,7 +3130,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3149,12 +3140,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3181,10 +3172,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804327</v>
+        <v>124804665</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3197,34 +3188,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437725</v>
+        <v>437783</v>
       </c>
       <c r="R23" t="n">
-        <v>7028254</v>
+        <v>7028272</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,10 +3298,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124803330</v>
+        <v>124806116</v>
       </c>
       <c r="B24" t="n">
-        <v>95335</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3310,25 +3310,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437842</v>
+        <v>437748</v>
       </c>
       <c r="R24" t="n">
-        <v>7028204</v>
+        <v>7028199</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124804266</v>
+        <v>124805623</v>
       </c>
       <c r="B25" t="n">
-        <v>95335</v>
+        <v>105102</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3431,21 +3431,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437728</v>
+        <v>437770</v>
       </c>
       <c r="R25" t="n">
-        <v>7028259</v>
+        <v>7028132</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124805471</v>
+        <v>124803938</v>
       </c>
       <c r="B4" t="n">
         <v>78891</v>
@@ -938,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437816</v>
+        <v>437774</v>
       </c>
       <c r="R4" t="n">
-        <v>7028222</v>
+        <v>7028215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124804327</v>
+        <v>124805275</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,34 +1045,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437725</v>
+        <v>437805</v>
       </c>
       <c r="R5" t="n">
-        <v>7028254</v>
+        <v>7028276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1123,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124803330</v>
+        <v>124803570</v>
       </c>
       <c r="B6" t="n">
-        <v>95335</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1167,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,13 +1195,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437842</v>
+        <v>437812</v>
       </c>
       <c r="R6" t="n">
-        <v>7028204</v>
+        <v>7028208</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,12 +1240,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804113</v>
+        <v>124804327</v>
       </c>
       <c r="B7" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,43 +1284,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437748</v>
+        <v>437725</v>
       </c>
       <c r="R7" t="n">
-        <v>7028228</v>
+        <v>7028254</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1357,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124805275</v>
+        <v>124805623</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>105102</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,47 +1401,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437805</v>
+        <v>437770</v>
       </c>
       <c r="R8" t="n">
-        <v>7028276</v>
+        <v>7028132</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,12 +1474,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1628,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124805701</v>
+        <v>124803330</v>
       </c>
       <c r="B10" t="n">
-        <v>79280</v>
+        <v>95335</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,25 +1635,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1797</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,13 +1663,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437772</v>
+        <v>437842</v>
       </c>
       <c r="R10" t="n">
-        <v>7028134</v>
+        <v>7028204</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1708,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803938</v>
+        <v>124804113</v>
       </c>
       <c r="B11" t="n">
-        <v>78891</v>
+        <v>105102</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,35 +1752,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>283</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1794,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437774</v>
+        <v>437748</v>
       </c>
       <c r="R11" t="n">
-        <v>7028215</v>
+        <v>7028228</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,12 +1830,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803570</v>
+        <v>124804266</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>95335</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,25 +1874,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1911,10 +1902,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437812</v>
+        <v>437728</v>
       </c>
       <c r="R12" t="n">
-        <v>7028208</v>
+        <v>7028259</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,7 +1937,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1956,12 +1947,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124803959</v>
+        <v>124804665</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,34 +1995,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437775</v>
+        <v>437783</v>
       </c>
       <c r="R13" t="n">
-        <v>7028228</v>
+        <v>7028272</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2105,10 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124804429</v>
+        <v>124804567</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2121,21 +2121,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437740</v>
+        <v>437764</v>
       </c>
       <c r="R14" t="n">
-        <v>7028260</v>
+        <v>7028274</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124803467</v>
+        <v>124806116</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437836</v>
+        <v>437748</v>
       </c>
       <c r="R15" t="n">
         <v>7028199</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2339,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124805601</v>
+        <v>124805471</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2355,27 +2355,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2384,10 +2388,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437787</v>
+        <v>437816</v>
       </c>
       <c r="R16" t="n">
-        <v>7028156</v>
+        <v>7028222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2419,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2429,12 +2433,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2461,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124804567</v>
+        <v>124804385</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,25 +2477,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2501,10 +2505,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437764</v>
+        <v>437727</v>
       </c>
       <c r="R17" t="n">
-        <v>7028274</v>
+        <v>7028271</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2536,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,12 +2550,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2578,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124804248</v>
+        <v>124805365</v>
       </c>
       <c r="B18" t="n">
-        <v>95347</v>
+        <v>91950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,21 +2598,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2813</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2618,10 +2622,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437722</v>
+        <v>437833</v>
       </c>
       <c r="R18" t="n">
-        <v>7028264</v>
+        <v>7028238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2653,7 +2657,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2663,7 +2667,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2695,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124804385</v>
+        <v>124805701</v>
       </c>
       <c r="B19" t="n">
-        <v>91457</v>
+        <v>79280</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2707,25 +2711,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>1797</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2735,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437727</v>
+        <v>437772</v>
       </c>
       <c r="R19" t="n">
-        <v>7028271</v>
+        <v>7028134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,7 +2774,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2780,12 +2784,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,10 +2816,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804266</v>
+        <v>124804248</v>
       </c>
       <c r="B20" t="n">
-        <v>95335</v>
+        <v>95347</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2828,21 +2832,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2852,10 +2856,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437728</v>
+        <v>437722</v>
       </c>
       <c r="R20" t="n">
-        <v>7028259</v>
+        <v>7028264</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2887,7 +2891,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2897,7 +2901,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2929,10 +2933,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124805365</v>
+        <v>124803959</v>
       </c>
       <c r="B21" t="n">
-        <v>91950</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,25 +2945,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2969,10 +2973,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437833</v>
+        <v>437775</v>
       </c>
       <c r="R21" t="n">
-        <v>7028238</v>
+        <v>7028228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3004,7 +3008,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3014,12 +3018,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3046,10 +3050,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124805959</v>
+        <v>124803467</v>
       </c>
       <c r="B22" t="n">
-        <v>78891</v>
+        <v>90977</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3058,50 +3062,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>283</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437768</v>
+        <v>437836</v>
       </c>
       <c r="R22" t="n">
-        <v>7028160</v>
+        <v>7028199</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3140,12 +3135,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3172,10 +3167,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804665</v>
+        <v>124804429</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3188,43 +3183,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437783</v>
+        <v>437740</v>
       </c>
       <c r="R23" t="n">
-        <v>7028272</v>
+        <v>7028260</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3256,7 +3242,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3266,12 +3252,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,10 +3284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124806116</v>
+        <v>124805959</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>78891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3314,37 +3300,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437748</v>
+        <v>437768</v>
       </c>
       <c r="R24" t="n">
-        <v>7028199</v>
+        <v>7028160</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3373,7 +3368,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3383,12 +3378,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,10 +3410,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124805623</v>
+        <v>124805601</v>
       </c>
       <c r="B25" t="n">
-        <v>105102</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3427,38 +3422,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437770</v>
+        <v>437787</v>
       </c>
       <c r="R25" t="n">
-        <v>7028132</v>
+        <v>7028156</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124803938</v>
+        <v>124805959</v>
       </c>
       <c r="B4" t="n">
         <v>78891</v>
@@ -938,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437774</v>
+        <v>437768</v>
       </c>
       <c r="R4" t="n">
-        <v>7028215</v>
+        <v>7028160</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805275</v>
+        <v>124805365</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,47 +1041,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437805</v>
+        <v>437833</v>
       </c>
       <c r="R5" t="n">
-        <v>7028276</v>
+        <v>7028238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124803570</v>
+        <v>124806116</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,21 +1162,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1195,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437812</v>
+        <v>437748</v>
       </c>
       <c r="R6" t="n">
-        <v>7028208</v>
+        <v>7028199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,12 +1231,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804327</v>
+        <v>124805701</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>79280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,21 +1279,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1797</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1312,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437725</v>
+        <v>437772</v>
       </c>
       <c r="R7" t="n">
-        <v>7028254</v>
+        <v>7028134</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,12 +1348,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124805623</v>
+        <v>124804429</v>
       </c>
       <c r="B8" t="n">
-        <v>105102</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,25 +1392,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437770</v>
+        <v>437740</v>
       </c>
       <c r="R8" t="n">
-        <v>7028132</v>
+        <v>7028260</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,12 +1465,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124803850</v>
+        <v>124803959</v>
       </c>
       <c r="B9" t="n">
-        <v>91950</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,25 +1509,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437757</v>
+        <v>437775</v>
       </c>
       <c r="R9" t="n">
-        <v>7028220</v>
+        <v>7028228</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,12 +1582,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,7 +1614,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124803330</v>
+        <v>124804266</v>
       </c>
       <c r="B10" t="n">
         <v>95335</v>
@@ -1663,13 +1654,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437842</v>
+        <v>437728</v>
       </c>
       <c r="R10" t="n">
-        <v>7028204</v>
+        <v>7028259</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1698,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1708,12 +1699,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804113</v>
+        <v>124803330</v>
       </c>
       <c r="B11" t="n">
-        <v>105102</v>
+        <v>95335</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1756,42 +1747,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437748</v>
+        <v>437842</v>
       </c>
       <c r="R11" t="n">
-        <v>7028228</v>
+        <v>7028204</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1816,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124804266</v>
+        <v>124804113</v>
       </c>
       <c r="B12" t="n">
-        <v>95335</v>
+        <v>105102</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,34 +1864,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437728</v>
+        <v>437748</v>
       </c>
       <c r="R12" t="n">
-        <v>7028259</v>
+        <v>7028228</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1947,12 +1938,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,10 +1970,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124804665</v>
+        <v>124803570</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,43 +1986,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437783</v>
+        <v>437812</v>
       </c>
       <c r="R13" t="n">
-        <v>7028272</v>
+        <v>7028208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2073,12 +2055,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2105,10 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124804567</v>
+        <v>124804665</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2121,34 +2103,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437764</v>
+        <v>437783</v>
       </c>
       <c r="R14" t="n">
-        <v>7028274</v>
+        <v>7028272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,12 +2181,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124806116</v>
+        <v>124804327</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2238,21 +2229,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2253,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437748</v>
+        <v>437725</v>
       </c>
       <c r="R15" t="n">
-        <v>7028199</v>
+        <v>7028254</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2307,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2339,7 +2330,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124805471</v>
+        <v>124803938</v>
       </c>
       <c r="B16" t="n">
         <v>78891</v>
@@ -2374,7 +2365,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2388,10 +2379,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437816</v>
+        <v>437774</v>
       </c>
       <c r="R16" t="n">
-        <v>7028222</v>
+        <v>7028215</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2423,7 +2414,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2433,12 +2424,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2465,10 +2456,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124804385</v>
+        <v>124804248</v>
       </c>
       <c r="B17" t="n">
-        <v>91457</v>
+        <v>95347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,25 +2468,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>2813</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2505,10 +2496,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437727</v>
+        <v>437722</v>
       </c>
       <c r="R17" t="n">
-        <v>7028271</v>
+        <v>7028264</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,7 +2531,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,12 +2541,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2582,10 +2573,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124805365</v>
+        <v>124805623</v>
       </c>
       <c r="B18" t="n">
-        <v>91950</v>
+        <v>105102</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2598,21 +2589,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2622,10 +2613,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437833</v>
+        <v>437770</v>
       </c>
       <c r="R18" t="n">
-        <v>7028238</v>
+        <v>7028132</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2667,12 +2658,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2699,10 +2690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124805701</v>
+        <v>124805471</v>
       </c>
       <c r="B19" t="n">
-        <v>79280</v>
+        <v>78891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,34 +2706,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1797</v>
+        <v>283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437772</v>
+        <v>437816</v>
       </c>
       <c r="R19" t="n">
-        <v>7028134</v>
+        <v>7028222</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,10 +2816,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804248</v>
+        <v>124804567</v>
       </c>
       <c r="B20" t="n">
-        <v>95347</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2828,25 +2828,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2813</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437722</v>
+        <v>437764</v>
       </c>
       <c r="R20" t="n">
-        <v>7028264</v>
+        <v>7028274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2933,10 +2933,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124803959</v>
+        <v>124805275</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,34 +2949,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437775</v>
+        <v>437805</v>
       </c>
       <c r="R21" t="n">
-        <v>7028228</v>
+        <v>7028276</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3008,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3018,12 +3027,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3050,10 +3059,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124803467</v>
+        <v>124803850</v>
       </c>
       <c r="B22" t="n">
-        <v>90977</v>
+        <v>91950</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3066,21 +3075,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3090,10 +3099,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437836</v>
+        <v>437757</v>
       </c>
       <c r="R22" t="n">
-        <v>7028199</v>
+        <v>7028220</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3125,7 +3134,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3135,12 +3144,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3167,10 +3176,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804429</v>
+        <v>124804385</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3179,25 +3188,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3207,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437740</v>
+        <v>437727</v>
       </c>
       <c r="R23" t="n">
-        <v>7028260</v>
+        <v>7028271</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3242,7 +3251,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3252,12 +3261,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,10 +3293,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124805959</v>
+        <v>124803467</v>
       </c>
       <c r="B24" t="n">
-        <v>78891</v>
+        <v>90977</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3296,50 +3305,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>283</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437768</v>
+        <v>437836</v>
       </c>
       <c r="R24" t="n">
-        <v>7028160</v>
+        <v>7028199</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124804266</v>
+        <v>124804113</v>
       </c>
       <c r="B10" t="n">
-        <v>95335</v>
+        <v>105102</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,34 +1630,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437728</v>
+        <v>437748</v>
       </c>
       <c r="R10" t="n">
-        <v>7028259</v>
+        <v>7028228</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,12 +1704,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,7 +1736,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803330</v>
+        <v>124804266</v>
       </c>
       <c r="B11" t="n">
         <v>95335</v>
@@ -1771,13 +1776,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437842</v>
+        <v>437728</v>
       </c>
       <c r="R11" t="n">
-        <v>7028204</v>
+        <v>7028259</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1811,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,12 +1821,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124804113</v>
+        <v>124803330</v>
       </c>
       <c r="B12" t="n">
-        <v>105102</v>
+        <v>95335</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,42 +1869,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437748</v>
+        <v>437842</v>
       </c>
       <c r="R12" t="n">
-        <v>7028228</v>
+        <v>7028204</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124805959</v>
+        <v>124805365</v>
       </c>
       <c r="B4" t="n">
-        <v>78891</v>
+        <v>91950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,50 +915,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437768</v>
+        <v>437833</v>
       </c>
       <c r="R4" t="n">
-        <v>7028160</v>
+        <v>7028238</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805365</v>
+        <v>124805959</v>
       </c>
       <c r="B5" t="n">
-        <v>91950</v>
+        <v>78891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,41 +1032,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437833</v>
+        <v>437768</v>
       </c>
       <c r="R5" t="n">
-        <v>7028238</v>
+        <v>7028160</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124806116</v>
+        <v>124805275</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,34 +1162,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437748</v>
+        <v>437805</v>
       </c>
       <c r="R6" t="n">
-        <v>7028199</v>
+        <v>7028276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,12 +1240,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124805701</v>
+        <v>124803959</v>
       </c>
       <c r="B7" t="n">
-        <v>79280</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,21 +1288,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1797</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1303,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437772</v>
+        <v>437775</v>
       </c>
       <c r="R7" t="n">
-        <v>7028134</v>
+        <v>7028228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,12 +1357,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804429</v>
+        <v>124804248</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>95347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,25 +1401,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1420,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437740</v>
+        <v>437722</v>
       </c>
       <c r="R8" t="n">
-        <v>7028260</v>
+        <v>7028264</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1474,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,7 +1506,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124803959</v>
+        <v>124803570</v>
       </c>
       <c r="B9" t="n">
         <v>91030</v>
@@ -1537,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437775</v>
+        <v>437812</v>
       </c>
       <c r="R9" t="n">
-        <v>7028228</v>
+        <v>7028208</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,7 +1581,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,12 +1591,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124804113</v>
+        <v>124804327</v>
       </c>
       <c r="B10" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,43 +1635,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437748</v>
+        <v>437725</v>
       </c>
       <c r="R10" t="n">
-        <v>7028228</v>
+        <v>7028254</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,12 +1708,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804266</v>
+        <v>124803467</v>
       </c>
       <c r="B11" t="n">
-        <v>95335</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,21 +1756,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1776,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437728</v>
+        <v>437836</v>
       </c>
       <c r="R11" t="n">
-        <v>7028259</v>
+        <v>7028199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1821,12 +1825,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,7 +1857,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803330</v>
+        <v>124804266</v>
       </c>
       <c r="B12" t="n">
         <v>95335</v>
@@ -1893,13 +1897,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437842</v>
+        <v>437728</v>
       </c>
       <c r="R12" t="n">
-        <v>7028204</v>
+        <v>7028259</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1928,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,12 +1942,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124803570</v>
+        <v>124805701</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>79280</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1986,21 +1990,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1797</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2010,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437812</v>
+        <v>437772</v>
       </c>
       <c r="R13" t="n">
-        <v>7028208</v>
+        <v>7028134</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,7 +2049,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,12 +2059,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124804665</v>
+        <v>124803330</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,50 +2103,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437783</v>
+        <v>437842</v>
       </c>
       <c r="R14" t="n">
-        <v>7028272</v>
+        <v>7028204</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2171,7 +2166,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,12 +2176,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124804327</v>
+        <v>124803938</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>78891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,34 +2224,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437725</v>
+        <v>437774</v>
       </c>
       <c r="R15" t="n">
-        <v>7028254</v>
+        <v>7028215</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,7 +2292,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,12 +2302,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2330,10 +2334,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124803938</v>
+        <v>124804385</v>
       </c>
       <c r="B16" t="n">
-        <v>78891</v>
+        <v>91457</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,47 +2346,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>283</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437774</v>
+        <v>437727</v>
       </c>
       <c r="R16" t="n">
-        <v>7028215</v>
+        <v>7028271</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,7 +2409,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2424,12 +2419,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2456,10 +2451,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124804248</v>
+        <v>124805623</v>
       </c>
       <c r="B17" t="n">
-        <v>95347</v>
+        <v>105102</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,21 +2467,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2813</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2496,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437722</v>
+        <v>437770</v>
       </c>
       <c r="R17" t="n">
-        <v>7028264</v>
+        <v>7028132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,7 +2526,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2541,12 +2536,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,10 +2568,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124805623</v>
+        <v>124804665</v>
       </c>
       <c r="B18" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2585,38 +2580,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437770</v>
+        <v>437783</v>
       </c>
       <c r="R18" t="n">
-        <v>7028132</v>
+        <v>7028272</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2648,7 +2652,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,12 +2662,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,10 +2694,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124805471</v>
+        <v>124803850</v>
       </c>
       <c r="B19" t="n">
-        <v>78891</v>
+        <v>91950</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,47 +2706,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437816</v>
+        <v>437757</v>
       </c>
       <c r="R19" t="n">
-        <v>7028222</v>
+        <v>7028220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2774,7 +2769,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2784,12 +2779,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804567</v>
+        <v>124806116</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2832,21 +2827,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2856,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437764</v>
+        <v>437748</v>
       </c>
       <c r="R20" t="n">
-        <v>7028274</v>
+        <v>7028199</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2891,7 +2886,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2901,12 +2896,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2933,10 +2928,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124805275</v>
+        <v>124804429</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,43 +2944,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437805</v>
+        <v>437740</v>
       </c>
       <c r="R21" t="n">
-        <v>7028276</v>
+        <v>7028260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3017,7 +3003,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,12 +3013,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3059,10 +3045,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124803850</v>
+        <v>124805601</v>
       </c>
       <c r="B22" t="n">
-        <v>91950</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3071,38 +3057,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437757</v>
+        <v>437787</v>
       </c>
       <c r="R22" t="n">
-        <v>7028220</v>
+        <v>7028156</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3134,7 +3125,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3144,12 +3135,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3176,10 +3167,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804385</v>
+        <v>124804567</v>
       </c>
       <c r="B23" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3188,25 +3179,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3207,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437727</v>
+        <v>437764</v>
       </c>
       <c r="R23" t="n">
-        <v>7028271</v>
+        <v>7028274</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3251,7 +3242,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3261,12 +3252,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3293,10 +3284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124803467</v>
+        <v>124804113</v>
       </c>
       <c r="B24" t="n">
-        <v>90977</v>
+        <v>105102</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3309,34 +3300,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437836</v>
+        <v>437748</v>
       </c>
       <c r="R24" t="n">
-        <v>7028199</v>
+        <v>7028228</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3368,7 +3364,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3378,12 +3374,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3410,10 +3406,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124805601</v>
+        <v>124805471</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>78891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3426,27 +3422,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437787</v>
+        <v>437816</v>
       </c>
       <c r="R25" t="n">
-        <v>7028156</v>
+        <v>7028222</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124805365</v>
+        <v>124805471</v>
       </c>
       <c r="B4" t="n">
-        <v>91950</v>
+        <v>78891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +915,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437833</v>
+        <v>437816</v>
       </c>
       <c r="R4" t="n">
-        <v>7028238</v>
+        <v>7028222</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1146,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124805275</v>
+        <v>124804113</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>105102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,35 +1167,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437805</v>
+        <v>437748</v>
       </c>
       <c r="R6" t="n">
-        <v>7028276</v>
+        <v>7028228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,12 +1245,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803959</v>
+        <v>124804429</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,21 +1293,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437775</v>
+        <v>437740</v>
       </c>
       <c r="R7" t="n">
-        <v>7028228</v>
+        <v>7028260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,12 +1362,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804248</v>
+        <v>124803570</v>
       </c>
       <c r="B8" t="n">
-        <v>95347</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,25 +1406,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2813</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437722</v>
+        <v>437812</v>
       </c>
       <c r="R8" t="n">
-        <v>7028264</v>
+        <v>7028208</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,12 +1479,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124803570</v>
+        <v>124805601</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,34 +1527,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437812</v>
+        <v>437787</v>
       </c>
       <c r="R9" t="n">
-        <v>7028208</v>
+        <v>7028156</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,7 +1591,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,12 +1601,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1740,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803467</v>
+        <v>124805365</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>91950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1756,21 +1766,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1790,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437836</v>
+        <v>437833</v>
       </c>
       <c r="R11" t="n">
-        <v>7028199</v>
+        <v>7028238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,7 +1825,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,12 +1835,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124804266</v>
+        <v>124805275</v>
       </c>
       <c r="B12" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,38 +1879,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437728</v>
+        <v>437805</v>
       </c>
       <c r="R12" t="n">
-        <v>7028259</v>
+        <v>7028276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,7 +1951,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1942,12 +1961,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,10 +1993,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124805701</v>
+        <v>124804665</v>
       </c>
       <c r="B13" t="n">
-        <v>79280</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,34 +2009,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437772</v>
+        <v>437783</v>
       </c>
       <c r="R13" t="n">
-        <v>7028134</v>
+        <v>7028272</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,7 +2077,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,12 +2087,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803330</v>
+        <v>124804248</v>
       </c>
       <c r="B14" t="n">
-        <v>95335</v>
+        <v>95347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,21 +2135,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,13 +2159,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437842</v>
+        <v>437722</v>
       </c>
       <c r="R14" t="n">
-        <v>7028204</v>
+        <v>7028264</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2166,7 +2194,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,12 +2204,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,10 +2236,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124803938</v>
+        <v>124803330</v>
       </c>
       <c r="B15" t="n">
-        <v>78891</v>
+        <v>95335</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,50 +2248,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>283</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437774</v>
+        <v>437842</v>
       </c>
       <c r="R15" t="n">
-        <v>7028215</v>
+        <v>7028204</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2292,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2302,12 +2321,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2334,10 +2353,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124804385</v>
+        <v>124804266</v>
       </c>
       <c r="B16" t="n">
-        <v>91457</v>
+        <v>95335</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,25 +2365,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2374,10 +2393,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437727</v>
+        <v>437728</v>
       </c>
       <c r="R16" t="n">
-        <v>7028271</v>
+        <v>7028259</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2409,7 +2428,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2419,12 +2438,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124805623</v>
+        <v>124803938</v>
       </c>
       <c r="B17" t="n">
-        <v>105102</v>
+        <v>78891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,38 +2482,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437770</v>
+        <v>437774</v>
       </c>
       <c r="R17" t="n">
-        <v>7028132</v>
+        <v>7028215</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2526,7 +2554,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2536,12 +2564,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2568,10 +2596,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124804665</v>
+        <v>124805623</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>105102</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,47 +2608,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437783</v>
+        <v>437770</v>
       </c>
       <c r="R18" t="n">
-        <v>7028272</v>
+        <v>7028132</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2652,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2662,12 +2681,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2811,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124806116</v>
+        <v>124803959</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,21 +2846,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2870,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437748</v>
+        <v>437775</v>
       </c>
       <c r="R20" t="n">
-        <v>7028199</v>
+        <v>7028228</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2886,7 +2905,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2896,12 +2915,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2928,10 +2947,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124804429</v>
+        <v>124804567</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2944,21 +2963,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2968,10 +2987,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437740</v>
+        <v>437764</v>
       </c>
       <c r="R21" t="n">
-        <v>7028260</v>
+        <v>7028274</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3003,7 +3022,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3013,12 +3032,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3045,10 +3064,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124805601</v>
+        <v>124803467</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3057,43 +3076,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437787</v>
+        <v>437836</v>
       </c>
       <c r="R22" t="n">
-        <v>7028156</v>
+        <v>7028199</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3125,7 +3139,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3135,12 +3149,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3167,10 +3181,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804567</v>
+        <v>124806116</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3183,21 +3197,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3207,10 +3221,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437764</v>
+        <v>437748</v>
       </c>
       <c r="R23" t="n">
-        <v>7028274</v>
+        <v>7028199</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3242,7 +3256,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3252,12 +3266,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,10 +3298,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124804113</v>
+        <v>124804385</v>
       </c>
       <c r="B24" t="n">
-        <v>105102</v>
+        <v>91457</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3296,43 +3310,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221725</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437748</v>
+        <v>437727</v>
       </c>
       <c r="R24" t="n">
-        <v>7028228</v>
+        <v>7028271</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3364,7 +3373,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3374,12 +3383,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3406,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124805471</v>
+        <v>124805701</v>
       </c>
       <c r="B25" t="n">
-        <v>78891</v>
+        <v>79280</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3422,43 +3431,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>283</v>
+        <v>1797</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437816</v>
+        <v>437772</v>
       </c>
       <c r="R25" t="n">
-        <v>7028222</v>
+        <v>7028134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124805471</v>
+        <v>124804327</v>
       </c>
       <c r="B4" t="n">
-        <v>78891</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,43 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437816</v>
+        <v>437725</v>
       </c>
       <c r="R4" t="n">
-        <v>7028222</v>
+        <v>7028254</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805959</v>
+        <v>124804567</v>
       </c>
       <c r="B5" t="n">
-        <v>78891</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,46 +1036,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437768</v>
+        <v>437764</v>
       </c>
       <c r="R5" t="n">
-        <v>7028160</v>
+        <v>7028274</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124804113</v>
+        <v>124803467</v>
       </c>
       <c r="B6" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,39 +1153,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437748</v>
+        <v>437836</v>
       </c>
       <c r="R6" t="n">
-        <v>7028228</v>
+        <v>7028199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,12 +1222,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804429</v>
+        <v>124804113</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>105102</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,38 +1266,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437740</v>
+        <v>437748</v>
       </c>
       <c r="R7" t="n">
-        <v>7028260</v>
+        <v>7028228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,12 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124803570</v>
+        <v>124803938</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>78891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,34 +1392,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437812</v>
+        <v>437774</v>
       </c>
       <c r="R8" t="n">
-        <v>7028208</v>
+        <v>7028215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124805601</v>
+        <v>124805959</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,27 +1518,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1556,13 +1551,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437787</v>
+        <v>437768</v>
       </c>
       <c r="R9" t="n">
-        <v>7028156</v>
+        <v>7028160</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1591,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,12 +1596,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124804327</v>
+        <v>124804266</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>95335</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,25 +1640,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437725</v>
+        <v>437728</v>
       </c>
       <c r="R10" t="n">
-        <v>7028254</v>
+        <v>7028259</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,12 +1713,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124805365</v>
+        <v>124805623</v>
       </c>
       <c r="B11" t="n">
-        <v>91950</v>
+        <v>105102</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,21 +1761,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437833</v>
+        <v>437770</v>
       </c>
       <c r="R11" t="n">
-        <v>7028238</v>
+        <v>7028132</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,12 +1830,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124805275</v>
+        <v>124805601</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,31 +1878,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1916,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437805</v>
+        <v>437787</v>
       </c>
       <c r="R12" t="n">
-        <v>7028276</v>
+        <v>7028156</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,7 +1942,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1961,12 +1952,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1993,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124804665</v>
+        <v>124805471</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2009,26 +2000,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2042,10 +2033,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437783</v>
+        <v>437816</v>
       </c>
       <c r="R13" t="n">
-        <v>7028272</v>
+        <v>7028222</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2077,7 +2068,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2087,12 +2078,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124804248</v>
+        <v>124803330</v>
       </c>
       <c r="B14" t="n">
-        <v>95347</v>
+        <v>95335</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,21 +2126,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2159,13 +2150,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437722</v>
+        <v>437842</v>
       </c>
       <c r="R14" t="n">
-        <v>7028264</v>
+        <v>7028204</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2194,7 +2185,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2204,12 +2195,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2236,10 +2227,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124803330</v>
+        <v>124803850</v>
       </c>
       <c r="B15" t="n">
-        <v>95335</v>
+        <v>91950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,21 +2243,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2276,13 +2267,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437842</v>
+        <v>437757</v>
       </c>
       <c r="R15" t="n">
-        <v>7028204</v>
+        <v>7028220</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2311,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,12 +2312,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,10 +2344,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124804266</v>
+        <v>124805275</v>
       </c>
       <c r="B16" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2365,38 +2356,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437728</v>
+        <v>437805</v>
       </c>
       <c r="R16" t="n">
-        <v>7028259</v>
+        <v>7028276</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124803938</v>
+        <v>124805365</v>
       </c>
       <c r="B17" t="n">
-        <v>78891</v>
+        <v>91950</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2482,47 +2482,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437774</v>
+        <v>437833</v>
       </c>
       <c r="R17" t="n">
-        <v>7028215</v>
+        <v>7028238</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2554,7 +2545,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2564,12 +2555,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2596,10 +2587,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124805623</v>
+        <v>124805701</v>
       </c>
       <c r="B18" t="n">
-        <v>105102</v>
+        <v>79280</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,25 +2599,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>1797</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2636,10 +2627,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437770</v>
+        <v>437772</v>
       </c>
       <c r="R18" t="n">
-        <v>7028132</v>
+        <v>7028134</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,12 +2672,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2713,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124803850</v>
+        <v>124803570</v>
       </c>
       <c r="B19" t="n">
-        <v>91950</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2725,25 +2716,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2753,10 +2744,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437757</v>
+        <v>437812</v>
       </c>
       <c r="R19" t="n">
-        <v>7028220</v>
+        <v>7028208</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2788,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2798,12 +2789,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2830,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124803959</v>
+        <v>124806116</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2846,21 +2837,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2870,10 +2861,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437775</v>
+        <v>437748</v>
       </c>
       <c r="R20" t="n">
-        <v>7028228</v>
+        <v>7028199</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2905,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2915,12 +2906,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2947,7 +2938,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124804567</v>
+        <v>124803959</v>
       </c>
       <c r="B21" t="n">
         <v>91030</v>
@@ -2987,10 +2978,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437764</v>
+        <v>437775</v>
       </c>
       <c r="R21" t="n">
-        <v>7028274</v>
+        <v>7028228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,7 +3013,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3032,7 +3023,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3064,10 +3055,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124803467</v>
+        <v>124804429</v>
       </c>
       <c r="B22" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3076,25 +3067,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3104,10 +3095,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437836</v>
+        <v>437740</v>
       </c>
       <c r="R22" t="n">
-        <v>7028199</v>
+        <v>7028260</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3139,7 +3130,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3149,7 +3140,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3181,10 +3172,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124806116</v>
+        <v>124804248</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>95347</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3193,25 +3184,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3221,10 +3212,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437748</v>
+        <v>437722</v>
       </c>
       <c r="R23" t="n">
-        <v>7028199</v>
+        <v>7028264</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3256,7 +3247,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3266,12 +3257,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,10 +3289,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124804385</v>
+        <v>124804665</v>
       </c>
       <c r="B24" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3310,38 +3301,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437727</v>
+        <v>437783</v>
       </c>
       <c r="R24" t="n">
-        <v>7028271</v>
+        <v>7028272</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124805701</v>
+        <v>124804385</v>
       </c>
       <c r="B25" t="n">
-        <v>79280</v>
+        <v>91457</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3427,25 +3427,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1797</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437772</v>
+        <v>437727</v>
       </c>
       <c r="R25" t="n">
-        <v>7028134</v>
+        <v>7028271</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124804266</v>
+        <v>124805623</v>
       </c>
       <c r="B10" t="n">
-        <v>95335</v>
+        <v>105102</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437728</v>
+        <v>437770</v>
       </c>
       <c r="R10" t="n">
-        <v>7028259</v>
+        <v>7028132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124805623</v>
+        <v>124804266</v>
       </c>
       <c r="B11" t="n">
-        <v>105102</v>
+        <v>95335</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437770</v>
+        <v>437728</v>
       </c>
       <c r="R11" t="n">
-        <v>7028132</v>
+        <v>7028259</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124804327</v>
+        <v>124804113</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +915,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437725</v>
+        <v>437748</v>
       </c>
       <c r="R4" t="n">
-        <v>7028254</v>
+        <v>7028228</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124804567</v>
+        <v>124805601</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1041,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437764</v>
+        <v>437787</v>
       </c>
       <c r="R5" t="n">
-        <v>7028274</v>
+        <v>7028156</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124803467</v>
+        <v>124803850</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>91950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1163,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437836</v>
+        <v>437757</v>
       </c>
       <c r="R6" t="n">
-        <v>7028199</v>
+        <v>7028220</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,12 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804113</v>
+        <v>124804567</v>
       </c>
       <c r="B7" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,43 +1276,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437748</v>
+        <v>437764</v>
       </c>
       <c r="R7" t="n">
-        <v>7028228</v>
+        <v>7028274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124803938</v>
+        <v>124804327</v>
       </c>
       <c r="B8" t="n">
-        <v>78891</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,43 +1397,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437774</v>
+        <v>437725</v>
       </c>
       <c r="R8" t="n">
-        <v>7028215</v>
+        <v>7028254</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124805959</v>
+        <v>124804266</v>
       </c>
       <c r="B9" t="n">
-        <v>78891</v>
+        <v>95335</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,50 +1510,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>283</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437768</v>
+        <v>437728</v>
       </c>
       <c r="R9" t="n">
-        <v>7028160</v>
+        <v>7028259</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,12 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124805623</v>
+        <v>124803330</v>
       </c>
       <c r="B10" t="n">
-        <v>105102</v>
+        <v>95335</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,21 +1631,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,13 +1655,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437770</v>
+        <v>437842</v>
       </c>
       <c r="R10" t="n">
-        <v>7028132</v>
+        <v>7028204</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1700,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804266</v>
+        <v>124803959</v>
       </c>
       <c r="B11" t="n">
-        <v>95335</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,25 +1744,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437728</v>
+        <v>437775</v>
       </c>
       <c r="R11" t="n">
-        <v>7028259</v>
+        <v>7028228</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1817,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124805601</v>
+        <v>124804665</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,27 +1865,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1907,10 +1898,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437787</v>
+        <v>437783</v>
       </c>
       <c r="R12" t="n">
-        <v>7028156</v>
+        <v>7028272</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1942,7 +1933,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1952,12 +1943,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,10 +1975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124805471</v>
+        <v>124804429</v>
       </c>
       <c r="B13" t="n">
-        <v>78891</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2000,43 +1991,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437816</v>
+        <v>437740</v>
       </c>
       <c r="R13" t="n">
-        <v>7028222</v>
+        <v>7028260</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2068,7 +2050,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2078,12 +2060,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,10 +2092,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803330</v>
+        <v>124804248</v>
       </c>
       <c r="B14" t="n">
-        <v>95335</v>
+        <v>95347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2126,21 +2108,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2150,13 +2132,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437842</v>
+        <v>437722</v>
       </c>
       <c r="R14" t="n">
-        <v>7028204</v>
+        <v>7028264</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2185,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2195,12 +2177,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2227,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124803850</v>
+        <v>124804385</v>
       </c>
       <c r="B15" t="n">
-        <v>91950</v>
+        <v>91457</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2239,25 +2221,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2267,10 +2249,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437757</v>
+        <v>437727</v>
       </c>
       <c r="R15" t="n">
-        <v>7028220</v>
+        <v>7028271</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,12 +2294,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2704,10 +2686,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124803570</v>
+        <v>124806116</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2720,21 +2702,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2744,10 +2726,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437812</v>
+        <v>437748</v>
       </c>
       <c r="R19" t="n">
-        <v>7028208</v>
+        <v>7028199</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2761,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2771,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2821,10 +2803,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124806116</v>
+        <v>124805959</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>78891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2837,37 +2819,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437748</v>
+        <v>437768</v>
       </c>
       <c r="R20" t="n">
-        <v>7028199</v>
+        <v>7028160</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2896,7 +2887,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2906,12 +2897,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,10 +2929,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124803959</v>
+        <v>124805623</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2950,25 +2941,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2978,10 +2969,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437775</v>
+        <v>437770</v>
       </c>
       <c r="R21" t="n">
-        <v>7028228</v>
+        <v>7028132</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3013,7 +3004,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3023,12 +3014,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,10 +3046,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124804429</v>
+        <v>124803570</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3071,21 +3062,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3095,10 +3086,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437740</v>
+        <v>437812</v>
       </c>
       <c r="R22" t="n">
-        <v>7028260</v>
+        <v>7028208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3130,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3140,12 +3131,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3172,10 +3163,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804248</v>
+        <v>124803467</v>
       </c>
       <c r="B23" t="n">
-        <v>95347</v>
+        <v>90977</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3188,21 +3179,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2813</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3212,10 +3203,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437722</v>
+        <v>437836</v>
       </c>
       <c r="R23" t="n">
-        <v>7028264</v>
+        <v>7028199</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3247,7 +3238,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3257,12 +3248,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,10 +3280,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124804665</v>
+        <v>124803938</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3305,26 +3296,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3338,10 +3329,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437783</v>
+        <v>437774</v>
       </c>
       <c r="R24" t="n">
-        <v>7028272</v>
+        <v>7028215</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3373,7 +3364,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3383,12 +3374,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,10 +3406,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124804385</v>
+        <v>124805471</v>
       </c>
       <c r="B25" t="n">
-        <v>91457</v>
+        <v>78891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3427,38 +3418,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437727</v>
+        <v>437816</v>
       </c>
       <c r="R25" t="n">
-        <v>7028271</v>
+        <v>7028222</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124804113</v>
+        <v>124803330</v>
       </c>
       <c r="B4" t="n">
-        <v>105102</v>
+        <v>95335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,42 +919,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437748</v>
+        <v>437842</v>
       </c>
       <c r="R4" t="n">
-        <v>7028228</v>
+        <v>7028204</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805601</v>
+        <v>124805365</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,43 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437787</v>
+        <v>437833</v>
       </c>
       <c r="R5" t="n">
-        <v>7028156</v>
+        <v>7028238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124803850</v>
+        <v>124804429</v>
       </c>
       <c r="B6" t="n">
-        <v>91950</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,25 +1149,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437757</v>
+        <v>437740</v>
       </c>
       <c r="R6" t="n">
-        <v>7028220</v>
+        <v>7028260</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1222,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804567</v>
+        <v>124803850</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>91950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,25 +1266,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437764</v>
+        <v>437757</v>
       </c>
       <c r="R7" t="n">
-        <v>7028274</v>
+        <v>7028220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1339,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804327</v>
+        <v>124805959</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>78891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,37 +1387,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437725</v>
+        <v>437768</v>
       </c>
       <c r="R8" t="n">
-        <v>7028254</v>
+        <v>7028160</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1465,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124804266</v>
+        <v>124804665</v>
       </c>
       <c r="B9" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,38 +1509,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437728</v>
+        <v>437783</v>
       </c>
       <c r="R9" t="n">
-        <v>7028259</v>
+        <v>7028272</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1581,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1591,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124803330</v>
+        <v>124804567</v>
       </c>
       <c r="B10" t="n">
-        <v>95335</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,25 +1635,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,13 +1663,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437842</v>
+        <v>437764</v>
       </c>
       <c r="R10" t="n">
-        <v>7028204</v>
+        <v>7028274</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,12 +1708,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803959</v>
+        <v>124804385</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,25 +1752,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1772,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437775</v>
+        <v>437727</v>
       </c>
       <c r="R11" t="n">
-        <v>7028228</v>
+        <v>7028271</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,12 +1825,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124804665</v>
+        <v>124805601</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,31 +1873,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437783</v>
+        <v>437787</v>
       </c>
       <c r="R12" t="n">
-        <v>7028272</v>
+        <v>7028156</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,7 +1937,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1943,12 +1947,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124804429</v>
+        <v>124804248</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>95347</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1987,25 +1991,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2015,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437740</v>
+        <v>437722</v>
       </c>
       <c r="R13" t="n">
-        <v>7028260</v>
+        <v>7028264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,7 +2054,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2060,12 +2064,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124804248</v>
+        <v>124804327</v>
       </c>
       <c r="B14" t="n">
-        <v>95347</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,25 +2108,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2813</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2132,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437722</v>
+        <v>437725</v>
       </c>
       <c r="R14" t="n">
-        <v>7028264</v>
+        <v>7028254</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2177,12 +2181,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2209,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124804385</v>
+        <v>124805471</v>
       </c>
       <c r="B15" t="n">
-        <v>91457</v>
+        <v>78891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,38 +2225,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437727</v>
+        <v>437816</v>
       </c>
       <c r="R15" t="n">
-        <v>7028271</v>
+        <v>7028222</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2297,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,12 +2307,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2452,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124805365</v>
+        <v>124806116</v>
       </c>
       <c r="B17" t="n">
-        <v>91950</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2464,25 +2477,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2492,10 +2505,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437833</v>
+        <v>437748</v>
       </c>
       <c r="R17" t="n">
-        <v>7028238</v>
+        <v>7028199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2527,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2537,12 +2550,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124805701</v>
+        <v>124804113</v>
       </c>
       <c r="B18" t="n">
-        <v>79280</v>
+        <v>105102</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2581,38 +2594,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1797</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437772</v>
+        <v>437748</v>
       </c>
       <c r="R18" t="n">
-        <v>7028134</v>
+        <v>7028228</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2654,12 +2672,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2686,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124806116</v>
+        <v>124805701</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>79280</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,21 +2720,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1797</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2726,10 +2744,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437748</v>
+        <v>437772</v>
       </c>
       <c r="R19" t="n">
-        <v>7028199</v>
+        <v>7028134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2771,12 +2789,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2803,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124805959</v>
+        <v>124803467</v>
       </c>
       <c r="B20" t="n">
-        <v>78891</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,50 +2833,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>283</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437768</v>
+        <v>437836</v>
       </c>
       <c r="R20" t="n">
-        <v>7028160</v>
+        <v>7028199</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2887,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2897,12 +2906,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2929,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124805623</v>
+        <v>124803570</v>
       </c>
       <c r="B21" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,25 +2950,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2969,10 +2978,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437770</v>
+        <v>437812</v>
       </c>
       <c r="R21" t="n">
-        <v>7028132</v>
+        <v>7028208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3004,7 +3013,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3014,12 +3023,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3046,10 +3055,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124803570</v>
+        <v>124805623</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3058,25 +3067,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3086,10 +3095,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437812</v>
+        <v>437770</v>
       </c>
       <c r="R22" t="n">
-        <v>7028208</v>
+        <v>7028132</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3121,7 +3130,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,12 +3140,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3163,10 +3172,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124803467</v>
+        <v>124803959</v>
       </c>
       <c r="B23" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3175,25 +3184,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3203,10 +3212,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437836</v>
+        <v>437775</v>
       </c>
       <c r="R23" t="n">
-        <v>7028199</v>
+        <v>7028228</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3238,7 +3247,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3248,12 +3257,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3280,10 +3289,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124803938</v>
+        <v>124804266</v>
       </c>
       <c r="B24" t="n">
-        <v>78891</v>
+        <v>95335</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3292,47 +3301,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>283</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437774</v>
+        <v>437728</v>
       </c>
       <c r="R24" t="n">
-        <v>7028215</v>
+        <v>7028259</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3406,7 +3406,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124805471</v>
+        <v>124803938</v>
       </c>
       <c r="B25" t="n">
         <v>78891</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437816</v>
+        <v>437774</v>
       </c>
       <c r="R25" t="n">
-        <v>7028222</v>
+        <v>7028215</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124803330</v>
+        <v>124803570</v>
       </c>
       <c r="B4" t="n">
-        <v>95335</v>
+        <v>91184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437842</v>
+        <v>437812</v>
       </c>
       <c r="R4" t="n">
-        <v>7028204</v>
+        <v>7028208</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805365</v>
+        <v>124805623</v>
       </c>
       <c r="B5" t="n">
-        <v>91950</v>
+        <v>105278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437833</v>
+        <v>437770</v>
       </c>
       <c r="R5" t="n">
-        <v>7028238</v>
+        <v>7028132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124804429</v>
+        <v>124806116</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437740</v>
+        <v>437748</v>
       </c>
       <c r="R6" t="n">
-        <v>7028260</v>
+        <v>7028199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803850</v>
+        <v>124803467</v>
       </c>
       <c r="B7" t="n">
-        <v>91950</v>
+        <v>91131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,21 +1270,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437757</v>
+        <v>437836</v>
       </c>
       <c r="R7" t="n">
-        <v>7028220</v>
+        <v>7028199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124805959</v>
+        <v>124804665</v>
       </c>
       <c r="B8" t="n">
-        <v>78891</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,26 +1387,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1420,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437768</v>
+        <v>437783</v>
       </c>
       <c r="R8" t="n">
-        <v>7028160</v>
+        <v>7028272</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124804665</v>
+        <v>124803330</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>95503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,50 +1509,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437783</v>
+        <v>437842</v>
       </c>
       <c r="R9" t="n">
-        <v>7028272</v>
+        <v>7028204</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,12 +1582,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124804567</v>
+        <v>124803850</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>92098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,25 +1626,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437764</v>
+        <v>437757</v>
       </c>
       <c r="R10" t="n">
-        <v>7028274</v>
+        <v>7028220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1708,12 +1699,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804385</v>
+        <v>124803938</v>
       </c>
       <c r="B11" t="n">
-        <v>91457</v>
+        <v>79028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,38 +1743,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437727</v>
+        <v>437774</v>
       </c>
       <c r="R11" t="n">
-        <v>7028271</v>
+        <v>7028215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124805601</v>
+        <v>124805365</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>92098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,43 +1869,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437787</v>
+        <v>437833</v>
       </c>
       <c r="R12" t="n">
-        <v>7028156</v>
+        <v>7028238</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1947,12 +1942,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124804248</v>
+        <v>124803959</v>
       </c>
       <c r="B13" t="n">
-        <v>95347</v>
+        <v>91184</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1991,25 +1986,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2813</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437722</v>
+        <v>437775</v>
       </c>
       <c r="R13" t="n">
-        <v>7028264</v>
+        <v>7028228</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,7 +2049,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2064,12 +2059,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124804327</v>
+        <v>124805959</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>79028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2112,37 +2107,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437725</v>
+        <v>437768</v>
       </c>
       <c r="R14" t="n">
-        <v>7028254</v>
+        <v>7028160</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2171,7 +2175,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,12 +2185,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124805471</v>
+        <v>124804113</v>
       </c>
       <c r="B15" t="n">
-        <v>78891</v>
+        <v>105278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,35 +2229,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>283</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437816</v>
+        <v>437748</v>
       </c>
       <c r="R15" t="n">
-        <v>7028222</v>
+        <v>7028228</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2342,7 +2342,7 @@
         <v>124805275</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124806116</v>
+        <v>124804429</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437748</v>
+        <v>437740</v>
       </c>
       <c r="R17" t="n">
-        <v>7028199</v>
+        <v>7028260</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2582,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124804113</v>
+        <v>124804385</v>
       </c>
       <c r="B18" t="n">
-        <v>105102</v>
+        <v>91617</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,43 +2594,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437748</v>
+        <v>437727</v>
       </c>
       <c r="R18" t="n">
-        <v>7028228</v>
+        <v>7028271</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,7 +2657,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2672,12 +2667,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2704,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124805701</v>
+        <v>124805471</v>
       </c>
       <c r="B19" t="n">
-        <v>79280</v>
+        <v>79028</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2720,34 +2715,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1797</v>
+        <v>283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437772</v>
+        <v>437816</v>
       </c>
       <c r="R19" t="n">
-        <v>7028134</v>
+        <v>7028222</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2783,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2793,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2821,10 +2825,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124803467</v>
+        <v>124804567</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>91184</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2833,25 +2837,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2861,10 +2865,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437836</v>
+        <v>437764</v>
       </c>
       <c r="R20" t="n">
-        <v>7028199</v>
+        <v>7028274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2896,7 +2900,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2906,12 +2910,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,10 +2942,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124803570</v>
+        <v>124804248</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>95515</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2950,25 +2954,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>2813</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2978,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437812</v>
+        <v>437722</v>
       </c>
       <c r="R21" t="n">
-        <v>7028208</v>
+        <v>7028264</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3013,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3023,12 +3027,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,10 +3059,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124805623</v>
+        <v>124804266</v>
       </c>
       <c r="B22" t="n">
-        <v>105102</v>
+        <v>95503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3071,21 +3075,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3095,10 +3099,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437770</v>
+        <v>437728</v>
       </c>
       <c r="R22" t="n">
-        <v>7028132</v>
+        <v>7028259</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3130,7 +3134,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3140,12 +3144,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3172,10 +3176,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124803959</v>
+        <v>124804327</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3212,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437775</v>
+        <v>437725</v>
       </c>
       <c r="R23" t="n">
-        <v>7028228</v>
+        <v>7028254</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3247,7 +3251,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3257,12 +3261,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,10 +3293,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124804266</v>
+        <v>124805701</v>
       </c>
       <c r="B24" t="n">
-        <v>95335</v>
+        <v>79417</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3301,25 +3305,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>1797</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3329,10 +3333,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437728</v>
+        <v>437772</v>
       </c>
       <c r="R24" t="n">
-        <v>7028259</v>
+        <v>7028134</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3364,7 +3368,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3374,12 +3378,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3406,10 +3410,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124803938</v>
+        <v>124805601</v>
       </c>
       <c r="B25" t="n">
-        <v>78891</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3422,31 +3426,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437774</v>
+        <v>437787</v>
       </c>
       <c r="R25" t="n">
-        <v>7028215</v>
+        <v>7028156</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3535,7 +3535,7 @@
         <v>124138438</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1731,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803938</v>
+        <v>124805365</v>
       </c>
       <c r="B11" t="n">
-        <v>79028</v>
+        <v>92098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,47 +1743,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437774</v>
+        <v>437833</v>
       </c>
       <c r="R11" t="n">
-        <v>7028215</v>
+        <v>7028238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,12 +1816,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124805365</v>
+        <v>124803959</v>
       </c>
       <c r="B12" t="n">
-        <v>92098</v>
+        <v>91184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,25 +1860,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1897,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437833</v>
+        <v>437775</v>
       </c>
       <c r="R12" t="n">
-        <v>7028238</v>
+        <v>7028228</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,7 +1923,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1942,12 +1933,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124803959</v>
+        <v>124803938</v>
       </c>
       <c r="B13" t="n">
-        <v>91184</v>
+        <v>79028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,34 +1981,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437775</v>
+        <v>437774</v>
       </c>
       <c r="R13" t="n">
-        <v>7028228</v>
+        <v>7028215</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124803570</v>
+        <v>124803938</v>
       </c>
       <c r="B4" t="n">
-        <v>91184</v>
+        <v>79028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +919,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437812</v>
+        <v>437774</v>
       </c>
       <c r="R4" t="n">
-        <v>7028208</v>
+        <v>7028215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805623</v>
+        <v>124804665</v>
       </c>
       <c r="B5" t="n">
-        <v>105278</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1041,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437770</v>
+        <v>437783</v>
       </c>
       <c r="R5" t="n">
-        <v>7028132</v>
+        <v>7028272</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1123,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124806116</v>
+        <v>124805701</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
+        <v>79417</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1171,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437748</v>
+        <v>437772</v>
       </c>
       <c r="R6" t="n">
-        <v>7028199</v>
+        <v>7028134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,12 +1240,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803467</v>
+        <v>124803959</v>
       </c>
       <c r="B7" t="n">
-        <v>91131</v>
+        <v>91184</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,25 +1284,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437836</v>
+        <v>437775</v>
       </c>
       <c r="R7" t="n">
-        <v>7028199</v>
+        <v>7028228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,12 +1357,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804665</v>
+        <v>124805623</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>105278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,47 +1401,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437783</v>
+        <v>437770</v>
       </c>
       <c r="R8" t="n">
-        <v>7028272</v>
+        <v>7028132</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1474,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124803330</v>
+        <v>124805959</v>
       </c>
       <c r="B9" t="n">
-        <v>95503</v>
+        <v>79028</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,41 +1518,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437842</v>
+        <v>437768</v>
       </c>
       <c r="R9" t="n">
-        <v>7028204</v>
+        <v>7028160</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,12 +1600,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog i nordsluttning</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124803850</v>
+        <v>124805601</v>
       </c>
       <c r="B10" t="n">
-        <v>92098</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,38 +1644,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437757</v>
+        <v>437787</v>
       </c>
       <c r="R10" t="n">
-        <v>7028220</v>
+        <v>7028156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,12 +1722,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124805365</v>
+        <v>124804327</v>
       </c>
       <c r="B11" t="n">
-        <v>92098</v>
+        <v>91184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,25 +1766,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,10 +1794,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437833</v>
+        <v>437725</v>
       </c>
       <c r="R11" t="n">
-        <v>7028238</v>
+        <v>7028254</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,7 +1829,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,12 +1839,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803959</v>
+        <v>124804385</v>
       </c>
       <c r="B12" t="n">
-        <v>91184</v>
+        <v>91617</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,25 +1883,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437775</v>
+        <v>437727</v>
       </c>
       <c r="R12" t="n">
-        <v>7028228</v>
+        <v>7028271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,7 +1946,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1933,12 +1956,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1988,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124803938</v>
+        <v>124804429</v>
       </c>
       <c r="B13" t="n">
-        <v>79028</v>
+        <v>91166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,43 +2004,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437774</v>
+        <v>437740</v>
       </c>
       <c r="R13" t="n">
-        <v>7028215</v>
+        <v>7028260</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,12 +2073,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen klen levande gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,10 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124805959</v>
+        <v>124805365</v>
       </c>
       <c r="B14" t="n">
-        <v>79028</v>
+        <v>92098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,50 +2117,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437768</v>
+        <v>437833</v>
       </c>
       <c r="R14" t="n">
-        <v>7028160</v>
+        <v>7028238</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2175,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2185,12 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2217,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124804113</v>
+        <v>124803467</v>
       </c>
       <c r="B15" t="n">
-        <v>105278</v>
+        <v>91131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2233,39 +2238,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437748</v>
+        <v>437836</v>
       </c>
       <c r="R15" t="n">
-        <v>7028228</v>
+        <v>7028199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2339,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124805275</v>
+        <v>124804266</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>95503</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2351,47 +2351,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437805</v>
+        <v>437728</v>
       </c>
       <c r="R16" t="n">
-        <v>7028276</v>
+        <v>7028259</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2423,7 +2414,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2433,12 +2424,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gamla granar (170-200 år) i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2465,10 +2456,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124804429</v>
+        <v>124803330</v>
       </c>
       <c r="B17" t="n">
-        <v>91166</v>
+        <v>95503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,25 +2468,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2505,13 +2496,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437740</v>
+        <v>437842</v>
       </c>
       <c r="R17" t="n">
-        <v>7028260</v>
+        <v>7028204</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2540,7 +2531,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,12 +2541,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2582,10 +2573,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124804385</v>
+        <v>124804567</v>
       </c>
       <c r="B18" t="n">
-        <v>91617</v>
+        <v>91184</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,25 +2585,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2622,10 +2613,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437727</v>
+        <v>437764</v>
       </c>
       <c r="R18" t="n">
-        <v>7028271</v>
+        <v>7028274</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2667,12 +2658,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granlåga i gammal bördig granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2699,10 +2690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124805471</v>
+        <v>124804113</v>
       </c>
       <c r="B19" t="n">
-        <v>79028</v>
+        <v>105278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2711,35 +2702,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2748,10 +2735,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437816</v>
+        <v>437748</v>
       </c>
       <c r="R19" t="n">
-        <v>7028222</v>
+        <v>7028228</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2783,7 +2770,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2793,12 +2780,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2825,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804567</v>
+        <v>124805471</v>
       </c>
       <c r="B20" t="n">
-        <v>91184</v>
+        <v>79028</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,34 +2828,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437764</v>
+        <v>437816</v>
       </c>
       <c r="R20" t="n">
-        <v>7028274</v>
+        <v>7028222</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2900,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2910,12 +2906,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2942,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124804248</v>
+        <v>124805275</v>
       </c>
       <c r="B21" t="n">
-        <v>95515</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2954,38 +2950,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437722</v>
+        <v>437805</v>
       </c>
       <c r="R21" t="n">
-        <v>7028264</v>
+        <v>7028276</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3017,7 +3022,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,12 +3032,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gamla granar (170-200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3059,10 +3064,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124804266</v>
+        <v>124803570</v>
       </c>
       <c r="B22" t="n">
-        <v>95503</v>
+        <v>91184</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3071,25 +3076,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3099,10 +3104,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437728</v>
+        <v>437812</v>
       </c>
       <c r="R22" t="n">
-        <v>7028259</v>
+        <v>7028208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3134,7 +3139,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3144,12 +3149,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3176,10 +3181,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804327</v>
+        <v>124806116</v>
       </c>
       <c r="B23" t="n">
-        <v>91184</v>
+        <v>91166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3192,21 +3197,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3216,10 +3221,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437725</v>
+        <v>437748</v>
       </c>
       <c r="R23" t="n">
-        <v>7028254</v>
+        <v>7028199</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3251,7 +3256,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3261,7 +3266,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3293,10 +3298,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124805701</v>
+        <v>124803850</v>
       </c>
       <c r="B24" t="n">
-        <v>79417</v>
+        <v>92098</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3305,25 +3310,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1797</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3333,10 +3338,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437772</v>
+        <v>437757</v>
       </c>
       <c r="R24" t="n">
-        <v>7028134</v>
+        <v>7028220</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3368,7 +3373,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3378,12 +3383,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran i gammal fuktig, bördig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3410,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124805601</v>
+        <v>124804248</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
+        <v>95515</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3422,43 +3427,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437787</v>
+        <v>437722</v>
       </c>
       <c r="R25" t="n">
-        <v>7028156</v>
+        <v>7028264</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1272,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803959</v>
+        <v>124805623</v>
       </c>
       <c r="B7" t="n">
-        <v>91184</v>
+        <v>105278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,25 +1284,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437775</v>
+        <v>437770</v>
       </c>
       <c r="R7" t="n">
-        <v>7028228</v>
+        <v>7028132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På marken i rikare gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124805623</v>
+        <v>124803959</v>
       </c>
       <c r="B8" t="n">
-        <v>105278</v>
+        <v>91184</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437770</v>
+        <v>437775</v>
       </c>
       <c r="R8" t="n">
-        <v>7028132</v>
+        <v>7028228</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i rikare gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124804113</v>
+        <v>124805471</v>
       </c>
       <c r="B19" t="n">
-        <v>105278</v>
+        <v>79028</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,31 +2702,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2735,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437748</v>
+        <v>437816</v>
       </c>
       <c r="R19" t="n">
-        <v>7028228</v>
+        <v>7028222</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,7 +2774,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2780,12 +2784,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,10 +2816,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124805471</v>
+        <v>124804113</v>
       </c>
       <c r="B20" t="n">
-        <v>79028</v>
+        <v>105278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,35 +2828,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>283</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437816</v>
+        <v>437748</v>
       </c>
       <c r="R20" t="n">
-        <v>7028222</v>
+        <v>7028228</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124805959</v>
+        <v>124805601</v>
       </c>
       <c r="B9" t="n">
-        <v>79028</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,31 +1522,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1555,13 +1551,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437768</v>
+        <v>437787</v>
       </c>
       <c r="R9" t="n">
-        <v>7028160</v>
+        <v>7028156</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,12 +1596,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
+          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124805601</v>
+        <v>124805959</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>79028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,27 +1644,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437787</v>
+        <v>437768</v>
       </c>
       <c r="R10" t="n">
-        <v>7028156</v>
+        <v>7028160</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på ca 170-årig, död gran i gammal granskog</t>
+          <t>På gren på lutande död gran vid källa i gammal fuktig, bördig granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124805471</v>
+        <v>124804113</v>
       </c>
       <c r="B19" t="n">
-        <v>79028</v>
+        <v>105278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,35 +2702,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2739,10 +2735,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437816</v>
+        <v>437748</v>
       </c>
       <c r="R19" t="n">
-        <v>7028222</v>
+        <v>7028228</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2774,7 +2770,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2784,12 +2780,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804113</v>
+        <v>124805471</v>
       </c>
       <c r="B20" t="n">
-        <v>105278</v>
+        <v>79028</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2828,31 +2824,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437748</v>
+        <v>437816</v>
       </c>
       <c r="R20" t="n">
-        <v>7028228</v>
+        <v>7028222</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På tunna kvistar på klen senvuxen gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>124805601</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>124805601</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>124805601</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3627,6 +3627,226 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128329438</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98390</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>437884</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7028187</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>VästraInneslänt (IS)Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128329299</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98390</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>437888</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7028207</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Extremt rikligt med Fläcknycklar VästraAllaMika Thunell</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -3632,7 +3632,7 @@
         <v>128329438</v>
       </c>
       <c r="B27" t="n">
-        <v>98390</v>
+        <v>98395</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>128329299</v>
       </c>
       <c r="B28" t="n">
-        <v>98390</v>
+        <v>98395</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -3632,7 +3632,7 @@
         <v>128329438</v>
       </c>
       <c r="B27" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>128329299</v>
       </c>
       <c r="B28" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -3632,7 +3632,7 @@
         <v>128329438</v>
       </c>
       <c r="B27" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>128329299</v>
       </c>
       <c r="B28" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -3632,7 +3632,7 @@
         <v>128329438</v>
       </c>
       <c r="B27" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>128329299</v>
       </c>
       <c r="B28" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -3632,7 +3632,7 @@
         <v>128329438</v>
       </c>
       <c r="B27" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>128329299</v>
       </c>
       <c r="B28" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -3632,7 +3632,7 @@
         <v>128329438</v>
       </c>
       <c r="B27" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>128329299</v>
       </c>
       <c r="B28" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -3632,7 +3632,7 @@
         <v>128329438</v>
       </c>
       <c r="B27" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>128329299</v>
       </c>
       <c r="B28" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -3632,7 +3632,7 @@
         <v>128329438</v>
       </c>
       <c r="B27" t="n">
-        <v>98536</v>
+        <v>98549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>128329299</v>
       </c>
       <c r="B28" t="n">
-        <v>98536</v>
+        <v>98549</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22078-2021 artfynd.xlsx
+++ b/artfynd/A 22078-2021 artfynd.xlsx
@@ -3632,7 +3632,7 @@
         <v>128329438</v>
       </c>
       <c r="B27" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>128329299</v>
       </c>
       <c r="B28" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
